--- a/artfynd/A 3952-2024 artfynd.xlsx
+++ b/artfynd/A 3952-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,122 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123236761</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56884</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102952</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tofsvipa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vanellus vanellus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Söderhagen VH, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>679867</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6554567</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristina Widgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristina Widgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3952-2024 artfynd.xlsx
+++ b/artfynd/A 3952-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,126 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123383287</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56821</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Söderhagen VH, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>679867</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6554567</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristina Widgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristina Widgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3952-2024 artfynd.xlsx
+++ b/artfynd/A 3952-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>123236761</v>
       </c>
       <c r="B3" t="n">
-        <v>56884</v>
+        <v>56887</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>123383287</v>
       </c>
       <c r="B4" t="n">
-        <v>56821</v>
+        <v>56824</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3952-2024 artfynd.xlsx
+++ b/artfynd/A 3952-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>123236761</v>
       </c>
       <c r="B3" t="n">
-        <v>56887</v>
+        <v>56893</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>123383287</v>
       </c>
       <c r="B4" t="n">
-        <v>56824</v>
+        <v>56830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3952-2024 artfynd.xlsx
+++ b/artfynd/A 3952-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>123236761</v>
       </c>
       <c r="B3" t="n">
-        <v>56893</v>
+        <v>56896</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>123383287</v>
       </c>
       <c r="B4" t="n">
-        <v>56830</v>
+        <v>56833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3952-2024 artfynd.xlsx
+++ b/artfynd/A 3952-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>123236761</v>
       </c>
       <c r="B3" t="n">
-        <v>56896</v>
+        <v>56897</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>123383287</v>
       </c>
       <c r="B4" t="n">
-        <v>56833</v>
+        <v>56834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
